--- a/delivery_order_templates/016_sandwich_order_form_template--delivery_order_templates.xlsx
+++ b/delivery_order_templates/016_sandwich_order_form_template--delivery_order_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates</t>
+          <t>bread_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sandwich Order Form</t>
+          <t>What type of bread would you like?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>delivery_order_templates_1</t>
+          <t>dietary_restrictions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Do you have any dietary restrictions?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_2</t>
+          <t>special_request</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Menu</t>
+          <t>Would you like to order extra?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_3</t>
+          <t>extra_cheese</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sandwich</t>
+          <t>Would you like extra cheese?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_4</t>
+          <t>extra_sauce</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Special Requests</t>
+          <t>Would you like extra sauce?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_5</t>
+          <t>delivery_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Special Requests</t>
+          <t>What is your preferred delivery time?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_6</t>
+          <t>preparation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sandwich</t>
+          <t>How would you like your sandwich to be prepared?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_7</t>
+          <t>toppings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sandwich</t>
+          <t>Do you want to add any toppings?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_8</t>
+          <t>extra_pickles</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sandwich</t>
+          <t>Would you like to order extra pickles?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,21 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_9</t>
+          <t>extra_olives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Would you like to order extra olives?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>extra_jalapenos</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Would you like to order extra jalapenos?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>side_dish</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Would you like to order a side dish?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -756,9 +802,9 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,204 +827,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>delivery_order_templates_1_choices</t>
+          <t>bread_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>whole_wheat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>whole wheat</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>delivery_order_templates_1_choices</t>
+          <t>bread_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>whole_white</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>whole white</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_2_choices</t>
+          <t>bread_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rye</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>rye</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_2_choices</t>
+          <t>dietary_restrictions_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>vegetarian</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_5_choices</t>
+          <t>dietary_restrictions_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>vegan</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_5_choices</t>
+          <t>dietary_restrictions_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>gluten_free</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>gluten free</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_6_choices</t>
+          <t>preparation_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>toasted</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>toasted</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_6_choices</t>
+          <t>preparation_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>grilled</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>grilled</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_7_choices</t>
+          <t>preparation_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>panini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>panini</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_7_choices</t>
+          <t>toppings_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>lettuce</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>lettuce</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_8_choices</t>
+          <t>toppings_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tomato</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>tomato</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sandwich_order_form_template_delivery_order_templates_8_choices</t>
+          <t>toppings_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>avocado</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>avocado</t>
         </is>
       </c>
     </row>
